--- a/data/g24-results-by-district.xlsx
+++ b/data/g24-results-by-district.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\sosfps3\Elections\Projects\Candidates &amp; Elections\SOV - SSOV\General 2024 SOV\SOV Exports\Formatted\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sachabondeville/Documents/stat133/Projects/Project-5/gerrymandering-sachabdvl/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF024573-F2DC-47EA-A198-44BBDDB62541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782555A1-496C-B441-914E-EA634E0EA684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Representative in Congress" sheetId="2" r:id="rId1"/>
@@ -1207,7 +1207,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1524,13 +1524,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF40D64E-EE75-4F39-BBF9-C2AB2E2FA1E8}">
   <dimension ref="A1:I546"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="10" t="s">
         <v>164</v>
       </c>
@@ -1543,7 +1543,7 @@
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="36" x14ac:dyDescent="0.15">
       <c r="B3" s="9" t="s">
         <v>216</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B4" s="8" t="s">
         <v>0</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>50979</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>4528</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>7197</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>9004</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>3009</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>61876</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>13229</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>25826</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>19281</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
         <v>18</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>13663</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
         <v>19</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>208592</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="6" t="s">
         <v>163</v>
       </c>
@@ -1691,12 +1691,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" s="4"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" s="10" t="s">
         <v>165</v>
       </c>
@@ -1709,7 +1709,7 @@
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
     </row>
-    <row r="21" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B21" s="9" t="s">
         <v>218</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B22" s="8" t="s">
         <v>0</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
         <v>22</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>5826</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>21666</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="s">
         <v>28</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>28012</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="5" t="s">
         <v>29</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>13808</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
         <v>31</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>34389</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A29" s="5" t="s">
         <v>34</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30" s="5" t="s">
         <v>19</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>106734</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A31" s="6" t="s">
         <v>163</v>
       </c>
@@ -1824,12 +1824,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A32" s="4"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A34" s="10" t="s">
         <v>166</v>
       </c>
@@ -1842,7 +1842,7 @@
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
     </row>
-    <row r="36" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="9" t="s">
         <v>319</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B37" s="8" t="s">
         <v>0</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A38" s="5" t="s">
         <v>35</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A39" s="5" t="s">
         <v>36</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>18052</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A40" s="5" t="s">
         <v>37</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>4660</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A41" s="5" t="s">
         <v>38</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>2503</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A42" s="5" t="s">
         <v>41</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>28004</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A43" s="5" t="s">
         <v>42</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>132825</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A44" s="5" t="s">
         <v>43</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>6044</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A45" s="5" t="s">
         <v>44</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>36075</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A46" s="5" t="s">
         <v>45</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A47" s="5" t="s">
         <v>18</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>4705</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A48" s="5" t="s">
         <v>19</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>234246</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A49" s="6" t="s">
         <v>163</v>
       </c>
@@ -1990,12 +1990,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A50" s="4"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A52" s="10" t="s">
         <v>167</v>
       </c>
@@ -2008,7 +2008,7 @@
       <c r="H52" s="10"/>
       <c r="I52" s="10"/>
     </row>
-    <row r="54" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B54" s="9" t="s">
         <v>221</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B55" s="8" t="s">
         <v>0</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A56" s="5" t="s">
         <v>48</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>12299</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A57" s="5" t="s">
         <v>49</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>19294</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A58" s="5" t="s">
         <v>50</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>31394</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A59" s="5" t="s">
         <v>31</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>30793</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A60" s="5" t="s">
         <v>52</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>21170</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A61" s="5" t="s">
         <v>19</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>114950</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A62" s="6" t="s">
         <v>163</v>
       </c>
@@ -2101,12 +2101,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A63" s="4"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A65" s="10" t="s">
         <v>168</v>
       </c>
@@ -2119,7 +2119,7 @@
       <c r="H65" s="10"/>
       <c r="I65" s="10"/>
     </row>
-    <row r="67" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" ht="36" x14ac:dyDescent="0.15">
       <c r="B67" s="9" t="s">
         <v>223</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B68" s="8" t="s">
         <v>0</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A69" s="5" t="s">
         <v>57</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>14607</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A70" s="5" t="s">
         <v>58</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>17051</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A71" s="5" t="s">
         <v>36</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>46898</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A72" s="5" t="s">
         <v>59</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>34642</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A73" s="5" t="s">
         <v>60</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>13128</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A74" s="5" t="s">
         <v>61</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>5786</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A75" s="5" t="s">
         <v>62</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>77587</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A76" s="5" t="s">
         <v>65</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>17944</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A77" s="5" t="s">
         <v>19</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>227643</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A78" s="6" t="s">
         <v>163</v>
       </c>
@@ -2245,12 +2245,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A79" s="4"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A81" s="10" t="s">
         <v>169</v>
       </c>
@@ -2263,7 +2263,7 @@
       <c r="H81" s="10"/>
       <c r="I81" s="10"/>
     </row>
-    <row r="83" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B83" s="9" t="s">
         <v>225</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B84" s="8" t="s">
         <v>0</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A85" s="5" t="s">
         <v>44</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>121664</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A86" s="5" t="s">
         <v>19</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>121664</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A87" s="6" t="s">
         <v>163</v>
       </c>
@@ -2312,12 +2312,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A88" s="4"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A90" s="10" t="s">
         <v>170</v>
       </c>
@@ -2330,7 +2330,7 @@
       <c r="H90" s="10"/>
       <c r="I90" s="10"/>
     </row>
-    <row r="92" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B92" s="9" t="s">
         <v>227</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B93" s="8" t="s">
         <v>0</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A94" s="5" t="s">
         <v>44</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>90406</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A95" s="5" t="s">
         <v>50</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A96" s="5" t="s">
         <v>52</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>7917</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A97" s="5" t="s">
         <v>19</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>98341</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A98" s="6" t="s">
         <v>163</v>
       </c>
@@ -2401,12 +2401,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A99" s="4"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A101" s="10" t="s">
         <v>171</v>
       </c>
@@ -2419,7 +2419,7 @@
       <c r="H101" s="10"/>
       <c r="I101" s="10"/>
     </row>
-    <row r="103" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B103" s="9" t="s">
         <v>229</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B104" s="8" t="s">
         <v>0</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A105" s="5" t="s">
         <v>70</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>33182</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A106" s="5" t="s">
         <v>50</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>37886</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A107" s="5" t="s">
         <v>19</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>71068</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A108" s="6" t="s">
         <v>163</v>
       </c>
@@ -2479,12 +2479,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A109" s="4"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A111" s="10" t="s">
         <v>172</v>
       </c>
@@ -2497,7 +2497,7 @@
       <c r="H111" s="10"/>
       <c r="I111" s="10"/>
     </row>
-    <row r="113" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B113" s="9" t="s">
         <v>231</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B114" s="8" t="s">
         <v>0</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A115" s="5" t="s">
         <v>70</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>4995</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A116" s="5" t="s">
         <v>73</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>115515</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A117" s="5" t="s">
         <v>62</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A118" s="5" t="s">
         <v>19</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>121174</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A119" s="6" t="s">
         <v>163</v>
       </c>
@@ -2568,12 +2568,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A120" s="4"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A122" s="10" t="s">
         <v>173</v>
       </c>
@@ -2586,7 +2586,7 @@
       <c r="H122" s="10"/>
       <c r="I122" s="10"/>
     </row>
-    <row r="124" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B124" s="9" t="s">
         <v>233</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B125" s="8" t="s">
         <v>0</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A126" s="5" t="s">
         <v>78</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>5983</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A127" s="5" t="s">
         <v>70</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>116236</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A128" s="5" t="s">
         <v>19</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>122219</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A129" s="6" t="s">
         <v>163</v>
       </c>
@@ -2646,12 +2646,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A130" s="4"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A132" s="10" t="s">
         <v>174</v>
       </c>
@@ -2664,7 +2664,7 @@
       <c r="H132" s="10"/>
       <c r="I132" s="10"/>
     </row>
-    <row r="134" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B134" s="9" t="s">
         <v>235</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B135" s="8" t="s">
         <v>0</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A136" s="5" t="s">
         <v>30</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>64315</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A137" s="5" t="s">
         <v>19</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>64315</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A138" s="6" t="s">
         <v>163</v>
       </c>
@@ -2713,12 +2713,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A139" s="4"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A141" s="10" t="s">
         <v>175</v>
       </c>
@@ -2731,7 +2731,7 @@
       <c r="H141" s="10"/>
       <c r="I141" s="10"/>
     </row>
-    <row r="143" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B143" s="9" t="s">
         <v>237</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B144" s="8" t="s">
         <v>0</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A145" s="5" t="s">
         <v>78</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>97849</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A146" s="5" t="s">
         <v>30</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A147" s="5" t="s">
         <v>19</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>97849</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A148" s="6" t="s">
         <v>163</v>
       </c>
@@ -2791,12 +2791,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A149" s="4"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A151" s="10" t="s">
         <v>176</v>
       </c>
@@ -2809,7 +2809,7 @@
       <c r="H151" s="10"/>
       <c r="I151" s="10"/>
     </row>
-    <row r="153" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B153" s="9" t="s">
         <v>239</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B154" s="8" t="s">
         <v>0</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A155" s="5" t="s">
         <v>59</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>11440</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A156" s="5" t="s">
         <v>60</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>19187</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A157" s="5" t="s">
         <v>81</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>40253</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A158" s="5" t="s">
         <v>73</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>6995</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A159" s="5" t="s">
         <v>62</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>27492</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A160" s="5" t="s">
         <v>19</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>105367</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A161" s="6" t="s">
         <v>163</v>
       </c>
@@ -2902,12 +2902,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A162" s="4"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A164" s="10" t="s">
         <v>177</v>
       </c>
@@ -2920,7 +2920,7 @@
       <c r="H164" s="10"/>
       <c r="I164" s="10"/>
     </row>
-    <row r="166" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B166" s="9" t="s">
         <v>241</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B167" s="8" t="s">
         <v>0</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A168" s="5" t="s">
         <v>78</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>89125</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A169" s="5" t="s">
         <v>19</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>89125</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A170" s="6" t="s">
         <v>163</v>
       </c>
@@ -2969,12 +2969,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A171" s="4"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A173" s="10" t="s">
         <v>178</v>
       </c>
@@ -2987,7 +2987,7 @@
       <c r="H173" s="10"/>
       <c r="I173" s="10"/>
     </row>
-    <row r="175" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B175" s="9" t="s">
         <v>243</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B176" s="8" t="s">
         <v>0</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A177" s="5" t="s">
         <v>30</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>10863</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A178" s="5" t="s">
         <v>86</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>67033</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A179" s="5" t="s">
         <v>19</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>77896</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A180" s="6" t="s">
         <v>163</v>
       </c>
@@ -3047,12 +3047,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A181" s="4"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A183" s="10" t="s">
         <v>179</v>
       </c>
@@ -3065,7 +3065,7 @@
       <c r="H183" s="10"/>
       <c r="I183" s="10"/>
     </row>
-    <row r="185" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B185" s="9" t="s">
         <v>245</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B186" s="8" t="s">
         <v>0</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A187" s="5" t="s">
         <v>86</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>22142</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A188" s="5" t="s">
         <v>89</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>106751</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A189" s="5" t="s">
         <v>19</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>128893</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A190" s="6" t="s">
         <v>163</v>
       </c>
@@ -3125,12 +3125,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A191" s="4"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A193" s="10" t="s">
         <v>180</v>
       </c>
@@ -3143,7 +3143,7 @@
       <c r="H193" s="10"/>
       <c r="I193" s="10"/>
     </row>
-    <row r="195" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B195" s="9" t="s">
         <v>247</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B196" s="8" t="s">
         <v>0</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A197" s="5" t="s">
         <v>78</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>13555</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A198" s="5" t="s">
         <v>89</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>68860</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A199" s="5" t="s">
         <v>19</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>82415</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A200" s="6" t="s">
         <v>163</v>
       </c>
@@ -3203,12 +3203,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A201" s="4"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A203" s="10" t="s">
         <v>181</v>
       </c>
@@ -3221,7 +3221,7 @@
       <c r="H203" s="10"/>
       <c r="I203" s="10"/>
     </row>
-    <row r="205" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B205" s="9" t="s">
         <v>249</v>
       </c>
@@ -3229,7 +3229,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B206" s="8" t="s">
         <v>0</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A207" s="5" t="s">
         <v>94</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>24585</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A208" s="5" t="s">
         <v>95</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>12119</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A209" s="5" t="s">
         <v>89</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>38620</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A210" s="5" t="s">
         <v>96</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A211" s="5" t="s">
         <v>19</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>80832</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A212" s="6" t="s">
         <v>163</v>
       </c>
@@ -3303,12 +3303,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A213" s="4"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A215" s="10" t="s">
         <v>182</v>
       </c>
@@ -3321,7 +3321,7 @@
       <c r="H215" s="10"/>
       <c r="I215" s="10"/>
     </row>
-    <row r="217" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B217" s="9" t="s">
         <v>251</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B218" s="8" t="s">
         <v>0</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A219" s="5" t="s">
         <v>94</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>21532</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A220" s="5" t="s">
         <v>99</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>28162</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A221" s="5" t="s">
         <v>89</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>40149</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A222" s="5" t="s">
         <v>96</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>22019</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A223" s="5" t="s">
         <v>19</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>111862</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A224" s="6" t="s">
         <v>163</v>
       </c>
@@ -3403,12 +3403,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A225" s="4"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A227" s="10" t="s">
         <v>183</v>
       </c>
@@ -3421,7 +3421,7 @@
       <c r="H227" s="10"/>
       <c r="I227" s="10"/>
     </row>
-    <row r="229" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:9" ht="24" x14ac:dyDescent="0.15">
       <c r="B229" s="9" t="s">
         <v>253</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B230" s="8" t="s">
         <v>1</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A231" s="5" t="s">
         <v>59</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>46702</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A232" s="5" t="s">
         <v>102</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>110314</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A233" s="5" t="s">
         <v>103</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>10402</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A234" s="5" t="s">
         <v>104</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>20444</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A235" s="5" t="s">
         <v>19</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>187862</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A236" s="6" t="s">
         <v>163</v>
       </c>
@@ -3503,12 +3503,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A237" s="4"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A239" s="10" t="s">
         <v>184</v>
       </c>
@@ -3521,7 +3521,7 @@
       <c r="H239" s="10"/>
       <c r="I239" s="10"/>
     </row>
-    <row r="241" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B241" s="9" t="s">
         <v>255</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B242" s="8" t="s">
         <v>0</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A243" s="5" t="s">
         <v>59</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>65297</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A244" s="5" t="s">
         <v>104</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>27436</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A245" s="5" t="s">
         <v>19</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>92733</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A246" s="6" t="s">
         <v>163</v>
       </c>
@@ -3581,12 +3581,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A247" s="4"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A249" s="10" t="s">
         <v>185</v>
       </c>
@@ -3599,7 +3599,7 @@
       <c r="H249" s="10"/>
       <c r="I249" s="10"/>
     </row>
-    <row r="251" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B251" s="9" t="s">
         <v>257</v>
       </c>
@@ -3607,7 +3607,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B252" s="8" t="s">
         <v>0</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A253" s="5" t="s">
         <v>102</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>54058</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A254" s="5" t="s">
         <v>103</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>10841</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A255" s="5" t="s">
         <v>104</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>24585</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A256" s="5" t="s">
         <v>19</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>89484</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A257" s="6" t="s">
         <v>163</v>
       </c>
@@ -3670,12 +3670,12 @@
         <v>112</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A258" s="4"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A260" s="10" t="s">
         <v>186</v>
       </c>
@@ -3688,7 +3688,7 @@
       <c r="H260" s="10"/>
       <c r="I260" s="10"/>
     </row>
-    <row r="262" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B262" s="9" t="s">
         <v>259</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B263" s="8" t="s">
         <v>0</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A264" s="5" t="s">
         <v>102</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>3127</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A265" s="5" t="s">
         <v>115</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>2406</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A266" s="5" t="s">
         <v>116</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>153753</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A267" s="5" t="s">
         <v>19</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>159286</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A268" s="6" t="s">
         <v>163</v>
       </c>
@@ -3759,12 +3759,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A269" s="4"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A271" s="10" t="s">
         <v>187</v>
       </c>
@@ -3777,7 +3777,7 @@
       <c r="H271" s="10"/>
       <c r="I271" s="10"/>
     </row>
-    <row r="273" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B273" s="9" t="s">
         <v>261</v>
       </c>
@@ -3785,7 +3785,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B274" s="8" t="s">
         <v>0</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A275" s="5" t="s">
         <v>99</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>36690</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A276" s="5" t="s">
         <v>119</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>65628</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A277" s="5" t="s">
         <v>120</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>25437</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A278" s="5" t="s">
         <v>19</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>127755</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A279" s="6" t="s">
         <v>163</v>
       </c>
@@ -3848,12 +3848,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A280" s="4"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A282" s="10" t="s">
         <v>188</v>
       </c>
@@ -3866,7 +3866,7 @@
       <c r="H282" s="10"/>
       <c r="I282" s="10"/>
     </row>
-    <row r="284" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B284" s="9" t="s">
         <v>263</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B285" s="8" t="s">
         <v>0</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A286" s="5" t="s">
         <v>121</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>23105</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A287" s="5" t="s">
         <v>122</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>82998</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A288" s="5" t="s">
         <v>116</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A289" s="5" t="s">
         <v>19</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>107194</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A290" s="6" t="s">
         <v>163</v>
       </c>
@@ -3937,12 +3937,12 @@
         <v>124</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A291" s="4"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A293" s="10" t="s">
         <v>189</v>
       </c>
@@ -3955,7 +3955,7 @@
       <c r="H293" s="10"/>
       <c r="I293" s="10"/>
     </row>
-    <row r="295" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B295" s="9" t="s">
         <v>265</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B296" s="8" t="s">
         <v>0</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A297" s="5" t="s">
         <v>115</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>11966</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A298" s="5" t="s">
         <v>120</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>134947</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A299" s="5" t="s">
         <v>19</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>146913</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A300" s="6" t="s">
         <v>163</v>
       </c>
@@ -4015,12 +4015,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A301" s="4"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A303" s="10" t="s">
         <v>190</v>
       </c>
@@ -4033,7 +4033,7 @@
       <c r="H303" s="10"/>
       <c r="I303" s="10"/>
     </row>
-    <row r="305" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B305" s="9" t="s">
         <v>267</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B306" s="8" t="s">
         <v>0</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A307" s="5" t="s">
         <v>115</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>146050</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A308" s="5" t="s">
         <v>19</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>146050</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A309" s="6" t="s">
         <v>163</v>
       </c>
@@ -4082,12 +4082,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A310" s="4"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A312" s="10" t="s">
         <v>191</v>
       </c>
@@ -4100,7 +4100,7 @@
       <c r="H312" s="10"/>
       <c r="I312" s="10"/>
     </row>
-    <row r="314" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B314" s="9" t="s">
         <v>269</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B315" s="8" t="s">
         <v>0</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A316" s="5" t="s">
         <v>115</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>86833</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A317" s="5" t="s">
         <v>116</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>23622</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A318" s="5" t="s">
         <v>19</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>110455</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A319" s="6" t="s">
         <v>163</v>
       </c>
@@ -4160,12 +4160,12 @@
         <v>128</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A320" s="4"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A322" s="10" t="s">
         <v>192</v>
       </c>
@@ -4178,7 +4178,7 @@
       <c r="H322" s="10"/>
       <c r="I322" s="10"/>
     </row>
-    <row r="324" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B324" s="9" t="s">
         <v>271</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B325" s="8" t="s">
         <v>0</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A326" s="5" t="s">
         <v>115</v>
       </c>
@@ -4205,7 +4205,7 @@
         <v>63374</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A327" s="5" t="s">
         <v>19</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>63374</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A328" s="6" t="s">
         <v>163</v>
       </c>
@@ -4227,12 +4227,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A329" s="4"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A331" s="10" t="s">
         <v>193</v>
       </c>
@@ -4245,7 +4245,7 @@
       <c r="H331" s="10"/>
       <c r="I331" s="10"/>
     </row>
-    <row r="333" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B333" s="9" t="s">
         <v>273</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B334" s="8" t="s">
         <v>0</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A335" s="5" t="s">
         <v>115</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>98559</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A336" s="5" t="s">
         <v>19</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>98559</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A337" s="6" t="s">
         <v>163</v>
       </c>
@@ -4294,12 +4294,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A338" s="4"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A340" s="10" t="s">
         <v>194</v>
       </c>
@@ -4312,7 +4312,7 @@
       <c r="H340" s="10"/>
       <c r="I340" s="10"/>
     </row>
-    <row r="342" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B342" s="9" t="s">
         <v>275</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B343" s="8" t="s">
         <v>0</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A344" s="5" t="s">
         <v>115</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>99856</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A345" s="5" t="s">
         <v>19</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>99856</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A346" s="6" t="s">
         <v>163</v>
       </c>
@@ -4361,12 +4361,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A347" s="4"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A349" s="10" t="s">
         <v>195</v>
       </c>
@@ -4379,7 +4379,7 @@
       <c r="H349" s="10"/>
       <c r="I349" s="10"/>
     </row>
-    <row r="351" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B351" s="9" t="s">
         <v>277</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B352" s="8" t="s">
         <v>0</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A353" s="5" t="s">
         <v>115</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>108165</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A354" s="5" t="s">
         <v>120</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A355" s="5" t="s">
         <v>19</v>
       </c>
@@ -4428,7 +4428,7 @@
         <v>108711</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A356" s="6" t="s">
         <v>163</v>
       </c>
@@ -4439,12 +4439,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A357" s="4"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A359" s="10" t="s">
         <v>196</v>
       </c>
@@ -4457,7 +4457,7 @@
       <c r="H359" s="10"/>
       <c r="I359" s="10"/>
     </row>
-    <row r="361" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B361" s="9" t="s">
         <v>279</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B362" s="8" t="s">
         <v>0</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A363" s="5" t="s">
         <v>116</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>96078</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A364" s="5" t="s">
         <v>19</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>96078</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A365" s="6" t="s">
         <v>163</v>
       </c>
@@ -4506,12 +4506,12 @@
         <v>136</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A366" s="4"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A368" s="10" t="s">
         <v>197</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="H368" s="10"/>
       <c r="I368" s="10"/>
     </row>
-    <row r="370" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B370" s="9" t="s">
         <v>281</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B371" s="8" t="s">
         <v>0</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A372" s="5" t="s">
         <v>115</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>84020</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A373" s="5" t="s">
         <v>19</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>84020</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A374" s="6" t="s">
         <v>163</v>
       </c>
@@ -4573,12 +4573,12 @@
         <v>138</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A375" s="4"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A377" s="10" t="s">
         <v>198</v>
       </c>
@@ -4591,7 +4591,7 @@
       <c r="H377" s="10"/>
       <c r="I377" s="10"/>
     </row>
-    <row r="379" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B379" s="9" t="s">
         <v>283</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B380" s="8" t="s">
         <v>0</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A381" s="5" t="s">
         <v>115</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>13234</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A382" s="5" t="s">
         <v>122</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>9336</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A383" s="5" t="s">
         <v>116</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>74572</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A384" s="5" t="s">
         <v>19</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>97142</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A385" s="6" t="s">
         <v>163</v>
       </c>
@@ -4662,12 +4662,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A386" s="4"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A388" s="10" t="s">
         <v>199</v>
       </c>
@@ -4680,7 +4680,7 @@
       <c r="H388" s="10"/>
       <c r="I388" s="10"/>
     </row>
-    <row r="390" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B390" s="9" t="s">
         <v>285</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B391" s="8" t="s">
         <v>0</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A392" s="5" t="s">
         <v>115</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>111985</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A393" s="5" t="s">
         <v>19</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>111985</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A394" s="6" t="s">
         <v>163</v>
       </c>
@@ -4729,12 +4729,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A395" s="4"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A397" s="10" t="s">
         <v>200</v>
       </c>
@@ -4747,7 +4747,7 @@
       <c r="H397" s="10"/>
       <c r="I397" s="10"/>
     </row>
-    <row r="399" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B399" s="9" t="s">
         <v>287</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B400" s="8" t="s">
         <v>0</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A401" s="5" t="s">
         <v>115</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>44450</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A402" s="5" t="s">
         <v>19</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>44450</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A403" s="6" t="s">
         <v>163</v>
       </c>
@@ -4796,12 +4796,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A404" s="4"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A406" s="10" t="s">
         <v>201</v>
       </c>
@@ -4814,7 +4814,7 @@
       <c r="H406" s="10"/>
       <c r="I406" s="10"/>
     </row>
-    <row r="408" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B408" s="9" t="s">
         <v>289</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B409" s="8" t="s">
         <v>0</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A410" s="5" t="s">
         <v>115</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>100019</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A411" s="5" t="s">
         <v>143</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>10799</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A412" s="5" t="s">
         <v>19</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>110818</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A413" s="6" t="s">
         <v>163</v>
       </c>
@@ -4874,12 +4874,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A414" s="4"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A416" s="10" t="s">
         <v>202</v>
       </c>
@@ -4892,7 +4892,7 @@
       <c r="H416" s="10"/>
       <c r="I416" s="10"/>
     </row>
-    <row r="418" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B418" s="9" t="s">
         <v>291</v>
       </c>
@@ -4900,7 +4900,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B419" s="8" t="s">
         <v>0</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A420" s="5" t="s">
         <v>122</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>99469</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A421" s="5" t="s">
         <v>19</v>
       </c>
@@ -4930,7 +4930,7 @@
         <v>99469</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A422" s="6" t="s">
         <v>163</v>
       </c>
@@ -4941,12 +4941,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A423" s="4"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A425" s="10" t="s">
         <v>203</v>
       </c>
@@ -4959,7 +4959,7 @@
       <c r="H425" s="10"/>
       <c r="I425" s="10"/>
     </row>
-    <row r="427" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B427" s="9" t="s">
         <v>293</v>
       </c>
@@ -4967,7 +4967,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B428" s="8" t="s">
         <v>0</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A429" s="5" t="s">
         <v>143</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>194398</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A430" s="5" t="s">
         <v>122</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>2685</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A431" s="5" t="s">
         <v>116</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>14915</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A432" s="5" t="s">
         <v>19</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>211998</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A433" s="6" t="s">
         <v>163</v>
       </c>
@@ -5030,12 +5030,12 @@
         <v>145</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A434" s="4"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A436" s="10" t="s">
         <v>204</v>
       </c>
@@ -5048,7 +5048,7 @@
       <c r="H436" s="10"/>
       <c r="I436" s="10"/>
     </row>
-    <row r="438" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B438" s="9" t="s">
         <v>295</v>
       </c>
@@ -5056,7 +5056,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B439" s="8" t="s">
         <v>0</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A440" s="5" t="s">
         <v>122</v>
       </c>
@@ -5075,7 +5075,7 @@
         <v>183216</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A441" s="5" t="s">
         <v>19</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>183216</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A442" s="6" t="s">
         <v>163</v>
       </c>
@@ -5097,12 +5097,12 @@
         <v>147</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A443" s="4"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A445" s="10" t="s">
         <v>205</v>
       </c>
@@ -5115,7 +5115,7 @@
       <c r="H445" s="10"/>
       <c r="I445" s="10"/>
     </row>
-    <row r="447" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B447" s="9" t="s">
         <v>297</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B448" s="8" t="s">
         <v>0</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A449" s="5" t="s">
         <v>115</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>74410</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A450" s="5" t="s">
         <v>19</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>74410</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A451" s="6" t="s">
         <v>163</v>
       </c>
@@ -5164,12 +5164,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A452" s="4"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A454" s="10" t="s">
         <v>206</v>
       </c>
@@ -5182,7 +5182,7 @@
       <c r="H454" s="10"/>
       <c r="I454" s="10"/>
     </row>
-    <row r="456" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B456" s="9" t="s">
         <v>299</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B457" s="8" t="s">
         <v>0</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A458" s="5" t="s">
         <v>115</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>53152</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A459" s="5" t="s">
         <v>19</v>
       </c>
@@ -5220,7 +5220,7 @@
         <v>53152</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A460" s="6" t="s">
         <v>163</v>
       </c>
@@ -5231,12 +5231,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A461" s="4"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A463" s="10" t="s">
         <v>207</v>
       </c>
@@ -5249,7 +5249,7 @@
       <c r="H463" s="10"/>
       <c r="I463" s="10"/>
     </row>
-    <row r="465" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B465" s="9" t="s">
         <v>301</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B466" s="8" t="s">
         <v>0</v>
       </c>
@@ -5265,7 +5265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A467" s="5" t="s">
         <v>115</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>66087</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A468" s="5" t="s">
         <v>19</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>66087</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A469" s="6" t="s">
         <v>163</v>
       </c>
@@ -5298,12 +5298,12 @@
         <v>151</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A470" s="4"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A472" s="10" t="s">
         <v>208</v>
       </c>
@@ -5316,7 +5316,7 @@
       <c r="H472" s="10"/>
       <c r="I472" s="10"/>
     </row>
-    <row r="474" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B474" s="9" t="s">
         <v>303</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B475" s="8" t="s">
         <v>0</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A476" s="5" t="s">
         <v>115</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>14840</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A477" s="5" t="s">
         <v>143</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>142771</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A478" s="5" t="s">
         <v>19</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>157611</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A479" s="6" t="s">
         <v>163</v>
       </c>
@@ -5376,12 +5376,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A480" s="4"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A482" s="10" t="s">
         <v>209</v>
       </c>
@@ -5394,7 +5394,7 @@
       <c r="H482" s="10"/>
       <c r="I482" s="10"/>
     </row>
-    <row r="484" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B484" s="9" t="s">
         <v>305</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B485" s="8" t="s">
         <v>0</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A486" s="5" t="s">
         <v>143</v>
       </c>
@@ -5421,7 +5421,7 @@
         <v>77279</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A487" s="5" t="s">
         <v>19</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>77279</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A488" s="6" t="s">
         <v>163</v>
       </c>
@@ -5443,12 +5443,12 @@
         <v>155</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A489" s="4"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A491" s="10" t="s">
         <v>210</v>
       </c>
@@ -5461,7 +5461,7 @@
       <c r="H491" s="10"/>
       <c r="I491" s="10"/>
     </row>
-    <row r="493" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B493" s="9" t="s">
         <v>307</v>
       </c>
@@ -5469,7 +5469,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B494" s="8" t="s">
         <v>0</v>
       </c>
@@ -5477,7 +5477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A495" s="5" t="s">
         <v>143</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>171554</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A496" s="5" t="s">
         <v>19</v>
       </c>
@@ -5499,7 +5499,7 @@
         <v>171554</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A497" s="6" t="s">
         <v>163</v>
       </c>
@@ -5510,12 +5510,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A498" s="4"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A500" s="10" t="s">
         <v>211</v>
       </c>
@@ -5528,7 +5528,7 @@
       <c r="H500" s="10"/>
       <c r="I500" s="10"/>
     </row>
-    <row r="502" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B502" s="9" t="s">
         <v>309</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B503" s="8" t="s">
         <v>0</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A504" s="5" t="s">
         <v>122</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>71149</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A505" s="5" t="s">
         <v>156</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>142476</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A506" s="5" t="s">
         <v>19</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>213625</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A507" s="6" t="s">
         <v>163</v>
       </c>
@@ -5588,12 +5588,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A508" s="4"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A510" s="10" t="s">
         <v>212</v>
       </c>
@@ -5606,7 +5606,7 @@
       <c r="H510" s="10"/>
       <c r="I510" s="10"/>
     </row>
-    <row r="512" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B512" s="9" t="s">
         <v>311</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B513" s="8" t="s">
         <v>0</v>
       </c>
@@ -5622,7 +5622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A514" s="5" t="s">
         <v>143</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>74512</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A515" s="5" t="s">
         <v>156</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>106438</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A516" s="5" t="s">
         <v>19</v>
       </c>
@@ -5655,7 +5655,7 @@
         <v>180950</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A517" s="6" t="s">
         <v>163</v>
       </c>
@@ -5666,12 +5666,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A518" s="4"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A520" s="10" t="s">
         <v>213</v>
       </c>
@@ -5684,7 +5684,7 @@
       <c r="H520" s="10"/>
       <c r="I520" s="10"/>
     </row>
-    <row r="522" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B522" s="9" t="s">
         <v>313</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B523" s="8" t="s">
         <v>0</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A524" s="5" t="s">
         <v>156</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>128859</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A525" s="5" t="s">
         <v>19</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>128859</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A526" s="6" t="s">
         <v>163</v>
       </c>
@@ -5733,12 +5733,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A527" s="4"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A529" s="10" t="s">
         <v>214</v>
       </c>
@@ -5751,7 +5751,7 @@
       <c r="H529" s="10"/>
       <c r="I529" s="10"/>
     </row>
-    <row r="531" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B531" s="9" t="s">
         <v>315</v>
       </c>
@@ -5759,7 +5759,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B532" s="8" t="s">
         <v>0</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A533" s="5" t="s">
         <v>156</v>
       </c>
@@ -5778,7 +5778,7 @@
         <v>128749</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A534" s="5" t="s">
         <v>19</v>
       </c>
@@ -5789,7 +5789,7 @@
         <v>128749</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A535" s="6" t="s">
         <v>163</v>
       </c>
@@ -5800,12 +5800,12 @@
         <v>162</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A536" s="4"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A538" s="10" t="s">
         <v>215</v>
       </c>
@@ -5818,7 +5818,7 @@
       <c r="H538" s="10"/>
       <c r="I538" s="10"/>
     </row>
-    <row r="540" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B540" s="9" t="s">
         <v>317</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B541" s="8" t="s">
         <v>0</v>
       </c>
@@ -5834,7 +5834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A542" s="5" t="s">
         <v>156</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>87501</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A543" s="5" t="s">
         <v>19</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>87501</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A544" s="6" t="s">
         <v>163</v>
       </c>
@@ -5867,24 +5867,52 @@
         <v>132</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A545" s="4"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A546" s="4"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A81:I81"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A52:I52"/>
-    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A510:I510"/>
+    <mergeCell ref="A520:I520"/>
+    <mergeCell ref="A529:I529"/>
+    <mergeCell ref="A538:I538"/>
+    <mergeCell ref="A454:I454"/>
+    <mergeCell ref="A463:I463"/>
+    <mergeCell ref="A472:I472"/>
+    <mergeCell ref="A482:I482"/>
+    <mergeCell ref="A491:I491"/>
+    <mergeCell ref="A500:I500"/>
+    <mergeCell ref="A445:I445"/>
+    <mergeCell ref="A340:I340"/>
+    <mergeCell ref="A349:I349"/>
+    <mergeCell ref="A359:I359"/>
+    <mergeCell ref="A368:I368"/>
+    <mergeCell ref="A377:I377"/>
+    <mergeCell ref="A388:I388"/>
+    <mergeCell ref="A397:I397"/>
+    <mergeCell ref="A406:I406"/>
+    <mergeCell ref="A416:I416"/>
+    <mergeCell ref="A425:I425"/>
+    <mergeCell ref="A436:I436"/>
+    <mergeCell ref="A331:I331"/>
+    <mergeCell ref="A215:I215"/>
+    <mergeCell ref="A227:I227"/>
+    <mergeCell ref="A239:I239"/>
+    <mergeCell ref="A249:I249"/>
+    <mergeCell ref="A260:I260"/>
+    <mergeCell ref="A271:I271"/>
+    <mergeCell ref="A282:I282"/>
+    <mergeCell ref="A293:I293"/>
+    <mergeCell ref="A303:I303"/>
+    <mergeCell ref="A312:I312"/>
+    <mergeCell ref="A322:I322"/>
     <mergeCell ref="A203:I203"/>
     <mergeCell ref="A90:I90"/>
     <mergeCell ref="A101:I101"/>
@@ -5897,40 +5925,12 @@
     <mergeCell ref="A173:I173"/>
     <mergeCell ref="A183:I183"/>
     <mergeCell ref="A193:I193"/>
-    <mergeCell ref="A331:I331"/>
-    <mergeCell ref="A215:I215"/>
-    <mergeCell ref="A227:I227"/>
-    <mergeCell ref="A239:I239"/>
-    <mergeCell ref="A249:I249"/>
-    <mergeCell ref="A260:I260"/>
-    <mergeCell ref="A271:I271"/>
-    <mergeCell ref="A282:I282"/>
-    <mergeCell ref="A293:I293"/>
-    <mergeCell ref="A303:I303"/>
-    <mergeCell ref="A312:I312"/>
-    <mergeCell ref="A322:I322"/>
-    <mergeCell ref="A445:I445"/>
-    <mergeCell ref="A340:I340"/>
-    <mergeCell ref="A349:I349"/>
-    <mergeCell ref="A359:I359"/>
-    <mergeCell ref="A368:I368"/>
-    <mergeCell ref="A377:I377"/>
-    <mergeCell ref="A388:I388"/>
-    <mergeCell ref="A397:I397"/>
-    <mergeCell ref="A406:I406"/>
-    <mergeCell ref="A416:I416"/>
-    <mergeCell ref="A425:I425"/>
-    <mergeCell ref="A436:I436"/>
-    <mergeCell ref="A510:I510"/>
-    <mergeCell ref="A520:I520"/>
-    <mergeCell ref="A529:I529"/>
-    <mergeCell ref="A538:I538"/>
-    <mergeCell ref="A454:I454"/>
-    <mergeCell ref="A463:I463"/>
-    <mergeCell ref="A472:I472"/>
-    <mergeCell ref="A482:I482"/>
-    <mergeCell ref="A491:I491"/>
-    <mergeCell ref="A500:I500"/>
+    <mergeCell ref="A81:I81"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A65:I65"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.75" header="0.25" footer="0.5"/>
